--- a/Assets/Tools/Luban/Datas/visual_asset.xlsx
+++ b/Assets/Tools/Luban/Datas/visual_asset.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TbVisualAsset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbVisualAsset" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>visual.missing.sprite</t>
@@ -487,7 +486,6504 @@
           <t>content/fallback/missing_card</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>visual.face.avatar.default</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>visual.face.help.armor_breaking_hammer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>visual.face.help.bear_trap</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>visual.face.help.blood_conversion</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>visual.face.help.blue_chest_card</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>visual.face.help.bomb</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>visual.face.help.brutality_card</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>visual.face.help.common_chest_card</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>visual.face.help.doubling_tower</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>visual.face.help.fireball</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>visual.face.help.flame</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>visual.face.help.food_card</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>visual.face.help.gold_card</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>visual.face.help.golden_chest_card</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>visual.face.help.healing_potion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>visual.face.help.healing_spring</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>visual.face.help.impact_tutorial</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>visual.face.help.kidnapping</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>visual.face.help.rolling_stone</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>visual.face.help.rotation_wheel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>visual.face.help.shield_bash_tutorial</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>visual.face.help.stat_boost_card</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>visual.face.help.sturdy_shield</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>visual.face.help.swap_card</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>visual.face.help.teleport_card</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>visual.face.help.throwing_knife</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>visual.face.help.ward_magic_card</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>visual.face.help.watchtower</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.beggar</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_19</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_orc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_128</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_skeleton</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_28</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.big_stone</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_99</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.bone_club_skeleton</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_14</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.bone_courier</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_34</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.brainless_orc</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_11</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.dragon_cult_leader</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_128</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.dragon_follower</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_104</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.executioner</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_82</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_bather</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_34</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_cult_leader</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_44</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_dragon</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_39</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_priest</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_67</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.fire_swallower</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_9</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.friendly_ancient</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_65</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.giant_skeleton</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_124</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.growing_stone</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_42</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.headless_skeleton</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_47</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.hoodlum</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_34</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.killer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_46</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.megalith</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_117</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.mist</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_106</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.multi_bone_worm</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_118</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.observer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_17</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.old_orc</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_12</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_boss</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_3</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_commander</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_127</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_quartermaster</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_85</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.orc_warrior</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_80</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.pickpocket</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_85</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.ringleader</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_69</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rogue</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_78</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rolling_stone_man</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_60</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.rotating_cub</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_39</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.salamander</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_64</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.sharp_stone</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_77</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.shelter_stone</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_36</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_king</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_18</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_mage</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_3</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skeleton_taunter</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_106</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.skull_head</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_68</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.sky_eye</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_35</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.smart_orc</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_115</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.smuggler</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_15</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.space_master</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_29</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stepwalker</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_106</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_golem</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_67</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_man</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_109</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_shrimp</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_65</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_swallower</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_11</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.stone_thrower</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_56</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.thug</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_101</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.vagrant</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_29</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.veteran_orc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_63</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.void_cub</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_117</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.void_lost</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_124</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.wandering_child</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_70</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.world_turning_hand</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_41</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>visual.icon.monster.young_orc</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack 1.png#pixel_art_card_pack 1_126</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>visual.face.deck.orc_legion</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>visual.face.deck.skeleton_legion</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>visual.face.deck.stone_legion</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>visual.face.deck.void</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>visual.face.deck.wandering_legion</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>visual.face.relic.craving</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>visual.face.relic.dragon_scale_armor</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>visual.face.relic.gold_armor</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>visual.face.relic.gold_knife</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>visual.face.relic.heavy_armor</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_coating</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_launcher</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_recycler</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>visual.face.relic.junk_slot_machine</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>visual.face.relic.lucky_coin</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>visual.face.relic.phoenix_feather</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>visual.face.relic.potion_bag</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>visual.face.relic.shield_knife</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>visual.face.relic.sling</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>visual.face.relic.throwing_knife_bag</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>visual.face.relic.vitality_amulet</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_armor</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_shield</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>visual.face.relic.wood_sword</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>visual.face.skill.absorb_bone</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>visual.face.skill.absorb_stone</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>visual.face.skill.air_strike</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>visual.face.skill.arsenal</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>visual.face.skill.battle_hardened</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>visual.face.skill.beggar_bond</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>visual.face.skill.blessing</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>visual.face.skill.bloodthirst</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>visual.face.skill.breathe_fire</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>visual.face.skill.call_followers</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>visual.face.skill.delivery</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>visual.face.skill.devotion</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>visual.face.skill.easy_road</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>visual.face.skill.even_hatred</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fall_apart</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>visual.face.skill.falling_rocks</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fight_me</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>visual.face.skill.find_weakness</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fire_power</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>visual.face.skill.first_strike</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>visual.face.skill.flame_boiling</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>visual.face.skill.flame_breath</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>visual.face.skill.fracture_fall_apart</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>visual.face.skill.gear_delivery</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>visual.face.skill.gift</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>visual.face.skill.give_punch</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>visual.face.skill.guide</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hard</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hard_skin</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hoodlum</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>visual.face.skill.hot_observation</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>visual.face.skill.intense_burning</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>visual.face.skill.learning_growth</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>visual.face.skill.love_fire</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>visual.face.skill.mixed_bones</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>visual.face.skill.monster_battle_hardened</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>visual.face.skill.orc_tactics</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>visual.face.skill.otherworld_help</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>visual.face.skill.random_walk</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>visual.face.skill.range_expand</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rascality</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>visual.face.skill.recombine_body</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>visual.face.skill.recombine_head</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>visual.face.skill.relentless_chase</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rolling_crush</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>visual.face.skill.rotate_lover</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>visual.face.skill.sacrifice</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>visual.face.skill.sharp_stone</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>visual.face.skill.smart</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>visual.face.skill.space_mastery</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stocking</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_growth</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_lover</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stone_shelter</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stray_cub</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>visual.face.skill.stroll</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>visual.face.skill.strong_combo</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>visual.face.skill.survival_wisdom</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>visual.face.skill.swallow_stone</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>visual.face.skill.taunt</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>visual.face.skill.thief_claims</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>visual.face.skill.thorn_skin</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>visual.face.skill.throw_stone</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>visual.face.skill.tower_child</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>visual.face.skill.turn_world</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>visual.face.skill.unstable</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>visual.face.skill.violence_maniac</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>visual.face.skill.violence_nutrition</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>visual.icon.avatar.default</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/character.png#character</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>visual.icon.help.armor_breaking_hammer</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/platform.png#platform</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>visual.icon.help.bear_trap</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/location_enemy.png#location_enemy</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>visual.icon.help.blood_conversion</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/sword_blood.png#sword_blood</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>visual.icon.help.blue_chest_card</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/arrow_blue_first.png#arrow_blue_first</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>visual.icon.help.bomb</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/bomb.png#bomb</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>visual.icon.help.brutality_card</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/voxel_paint.png#voxel_paint</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>visual.icon.help.common_chest_card</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/chest.png#chest</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>visual.icon.help.doubling_tower</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/widget_width.png#widget_width</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>visual.icon.help.fireball</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/dialogue_page.png#dialogue_page</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>visual.icon.help.flame</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/keyboard.png#keyboard</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>visual.icon.help.food_card</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/light_energy.png#light_energy</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>visual.icon.help.gold_card</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/light.png#light</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>visual.icon.help.golden_chest_card</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/chest.png#chest</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>visual.icon.help.healing_potion</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/potion.png#potion</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>visual.icon.help.healing_spring</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/tree_collapse.png#tree_collapse</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>visual.icon.help.impact_tutorial</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/clock.png#clock</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>visual.icon.help.kidnapping</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/terrain_precise.png#terrain_precise</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>visual.icon.help.rolling_stone</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/portrait_left.png#portrait_left</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>visual.icon.help.rotation_wheel</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/widget_width.png#widget_width</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>visual.icon.help.shield_bash_tutorial</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/shield.png#shield</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>visual.icon.help.stat_boost_card</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/character_add.png#character_add</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>visual.icon.help.sturdy_shield</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/shield.png#shield</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>visual.icon.help.swap_card</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/mac_logo.png#mac_logo</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>visual.icon.help.teleport_card</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/number.png#number</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>visual.icon.help.throwing_knife</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/widget.png#widget</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>visual.icon.help.ward_magic_card</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/anim_frame_move_right.png#anim_frame_move_right</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>visual.icon.help.watchtower</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/voxel_outlines.png#voxel_outlines</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>visual.face.monster.beggar</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>visual.face.monster.big_orc</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>visual.face.monster.big_skeleton</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>visual.face.monster.big_stone</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>visual.face.monster.bone_club_skeleton</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>visual.face.monster.bone_courier</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>visual.face.monster.brainless_orc</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>visual.face.monster.dragon_cult_leader</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>visual.face.monster.dragon_follower</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>visual.face.monster.executioner</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>visual.face.monster.fire_bather</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>visual.face.monster.fire_cult_leader</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>visual.face.monster.fire_dragon</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>visual.face.monster.fire_priest</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>visual.face.monster.fire_swallower</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>visual.face.monster.friendly_ancient</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>visual.face.monster.giant_skeleton</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>visual.face.monster.growing_stone</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>visual.face.monster.headless_skeleton</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>visual.face.monster.hoodlum</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>visual.face.monster.killer</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>visual.face.monster.megalith</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>visual.face.monster.mist</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>visual.face.monster.multi_bone_worm</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>visual.face.monster.observer</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>visual.face.monster.old_orc</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>visual.face.monster.orc_boss</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>visual.face.monster.orc_commander</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>visual.face.monster.orc_quartermaster</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>visual.face.monster.orc_warrior</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>visual.face.monster.pickpocket</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>visual.face.monster.ringleader</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>visual.face.monster.rogue</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>visual.face.monster.rolling_stone_man</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>visual.face.monster.rotating_cub</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>visual.face.monster.salamander</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>visual.face.monster.sharp_stone</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>visual.face.monster.shelter_stone</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>visual.face.monster.skeleton_king</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>visual.face.monster.skeleton_mage</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>visual.face.monster.skeleton_taunter</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>visual.face.monster.skull_head</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_5</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>visual.face.monster.sky_eye</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>visual.face.monster.smart_orc</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>visual.face.monster.smuggler</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>visual.face.monster.space_master</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stepwalker</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stone_golem</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stone_man</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_7</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stone_shrimp</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stone_swallower</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>visual.face.monster.stone_thrower</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_10</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>visual.face.monster.thug</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>visual.face.monster.vagrant</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_8</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>visual.face.monster.veteran_orc</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>visual.face.monster.void_cub</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_6</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>visual.face.monster.void_lost</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_2</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>visual.face.monster.wandering_child</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_3</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>visual.face.monster.world_turning_hand</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_1</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>visual.face.monster.young_orc</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_4</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>visual.face.deck.dragon</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Multiple/pixel_art_card_pack.png#pixel_art_card_pack_9</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.craving</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/jewel.png#jewel</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.dragon_scale_armor</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/magic_wand.png#magic_wand</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.gold_armor</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dice.png#dice</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.gold_knife</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/letter_tile.png#letter_tile</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.heavy_armor</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/billiard_rack.png#billiard_rack</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_coating</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/flag_piece.png#flag_piece</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_launcher</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/bowling_pin.png#bowling_pin</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_recycler</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/coins.png#coins</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.junk_slot_machine</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dice_5.png#dice_5</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.lucky_coin</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/coins.png#coins</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.phoenix_feather</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/coins.png#coins</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.potion_bag</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/connect.png#connect</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.shield_knife</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/card.png#card</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.sling</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/hash.png#hash</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.throwing_knife_bag</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/pound.png#pound</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.vitality_amulet</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/rook.png#rook</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_armor</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/jewel.png#jewel</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_shield</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/billiard_rack.png#billiard_rack</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>visual.icon.relic.wood_sword</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/spade.png#spade</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>visual.icon.Fountain</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/arrow_refresh.png#arrow_refresh</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>visual.icon.Gold</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/wizard.png#wizard</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>visual.icon.Shop</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/anim_frame_delete.png#anim_frame_delete</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>visual.icon.Tavern</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/map.png#map</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>visual.icon.Treasure</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Items/arrow_up_down.png#arrow_up_down</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.absorb_bone</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/spinner.png#spinner</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.absorb_stone</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/spade_outline.png#spade_outline</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.air_strike</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/letter_tile.png#letter_tile</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.arsenal</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/rook.png#rook</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.battle_hardened</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/bowling_pins.png#bowling_pins</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.beggar_bond</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/heart_outline.png#heart_outline</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.blessing</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/domino_diagonal.png#domino_diagonal</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.bloodthirst</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/house.png#house</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.breathe_fire</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dice_1.png#dice_1</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.call_followers</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/magic_wand.png#magic_wand</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.delivery</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/letter_tile.png#letter_tile</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.devotion</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/pawn.png#pawn</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.easy_road</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/yen.png#yen</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.even_hatred</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/seven.png#seven</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fall_apart</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dice.png#dice</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.falling_rocks</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/club.png#club</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fight_me</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/card.png#card</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.find_weakness</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/connect.png#connect</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fire_power</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/piece.png#piece</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.first_strike</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/cards.png#cards</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.flame_boiling</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/suits.png#suits</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.flame_breath</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/coins.png#coins</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.fracture_fall_apart</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/heart_outline.png#heart_outline</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.gear_delivery</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/deck.png#deck</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.gift</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/mahjong_tiles.png#mahjong_tiles</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.give_punch</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/house.png#house</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.guide</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/heart.png#heart</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hard</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/yen.png#yen</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hard_skin</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/spinner.png#spinner</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hoodlum</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/mahjong_tile.png#mahjong_tile</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.hot_observation</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/billiard_rack.png#billiard_rack</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.intense_burning</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/piece.png#piece</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.learning_growth</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/piece.png#piece</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.love_fire</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/bowling_pins.png#bowling_pins</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.mixed_bones</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/billiard_rack.png#billiard_rack</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.monster_battle_hardened</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/bowling_pins.png#bowling_pins</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.orc_tactics</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/bishop.png#bishop</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.otherworld_help</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/star.png#star</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.random_walk</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/bowling_ball.png#bowling_ball</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.range_expand</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/flag_piece.png#flag_piece</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rascality</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/club.png#club</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.recombine_body</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/mahjong_tile.png#mahjong_tile</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.recombine_head</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/deck.png#deck</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.relentless_chase</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/billiard.png#billiard</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rolling_crush</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/knight.png#knight</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.rotate_lover</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/bowling_pin.png#bowling_pin</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.sacrifice</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/mahjong_tile.png#mahjong_tile</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.sharp_stone</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/domino_diagonal.png#domino_diagonal</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.smart</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/bowling_ball.png#bowling_ball</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.space_mastery</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dominoes.png#dominoes</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stocking</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/king.png#king</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_growth</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/dice_1.png#dice_1</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_lover</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/joker.png#joker</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stone_shelter</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/mahjong_tiles.png#mahjong_tiles</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stray_cub</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/club.png#club</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.stroll</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/piece.png#piece</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.strong_combo</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/domino_diagonal.png#domino_diagonal</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.survival_wisdom</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/deck.png#deck</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.swallow_stone</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/club_outline.png#club_outline</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.taunt</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/flag_piece.png#flag_piece</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.thief_claims</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/domino.png#domino</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.thorn_skin</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/bowling_ball.png#bowling_ball</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.throw_stone</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/seven.png#seven</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.tower_child</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/checkerboard.png#checkerboard</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.turn_world</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/cards.png#cards</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.unstable</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/heart_outline.png#heart_outline</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.violence_maniac</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/blue_2d/mahjong_tiles.png#mahjong_tiles</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>visual.icon.skill.violence_nutrition</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>sprite</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Assets/Arts/Images/Png/Icons/white_node/spinner.png#spinner</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
